--- a/exports/trend_1d/HAL_full_report.xlsx
+++ b/exports/trend_1d/HAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H2" t="n">
-        <v>541.6</v>
+        <v>533.2</v>
       </c>
       <c r="I2" t="n">
         <v>533.380805</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.54</v>
+        <v>-5.04</v>
       </c>
       <c r="L2" t="n">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="M2" t="n">
         <v>0.48</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>6.95</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43249</v>
+        <v>43250</v>
       </c>
       <c r="H3" t="n">
-        <v>524.35</v>
+        <v>540.7</v>
       </c>
       <c r="I3" t="n">
         <v>534.1545323379189</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>1.66</v>
+        <v>-1.41</v>
       </c>
       <c r="L3" t="n">
-        <v>2.03</v>
+        <v>2.96</v>
       </c>
       <c r="M3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>3.12</v>
       </c>
       <c r="O3" t="n">
         <v>-1.55</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.01</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H4" t="n">
-        <v>493.55</v>
+        <v>486.9</v>
       </c>
       <c r="I4" t="n">
         <v>491.8885636997823</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.720000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>9.01</v>
+        <v>10.42</v>
       </c>
       <c r="M4" t="n">
         <v>0.67</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.92</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H5" t="n">
-        <v>394.65</v>
+        <v>445.1</v>
       </c>
       <c r="I5" t="n">
         <v>415.7100482098063</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
-        <v>18.95</v>
+        <v>8.58</v>
       </c>
       <c r="L5" t="n">
         <v>3.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>12.78</v>
       </c>
       <c r="O5" t="n">
         <v>-1.35</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.05</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H6" t="n">
-        <v>443.9</v>
+        <v>434.35</v>
       </c>
       <c r="I6" t="n">
         <v>440.0850579831873</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.27</v>
+        <v>-2.42</v>
       </c>
       <c r="L6" t="n">
         <v>11.14</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.02</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43357</v>
+        <v>43360</v>
       </c>
       <c r="H7" t="n">
-        <v>466.15</v>
+        <v>476.6</v>
       </c>
       <c r="I7" t="n">
         <v>471.5211727690967</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.32</v>
+        <v>-9.73</v>
       </c>
       <c r="L7" t="n">
-        <v>8.779999999999999</v>
+        <v>10.51</v>
       </c>
       <c r="M7" t="n">
         <v>0.77</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43367</v>
+        <v>43368</v>
       </c>
       <c r="H8" t="n">
-        <v>435.95</v>
+        <v>421.1</v>
       </c>
       <c r="I8" t="n">
         <v>429.6484574476766</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.529999999999999</v>
+        <v>-11.64</v>
       </c>
       <c r="L8" t="n">
-        <v>9.199999999999999</v>
+        <v>12.04</v>
       </c>
       <c r="M8" t="n">
         <v>1.64</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>15.2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H9" t="n">
-        <v>383.15</v>
+        <v>459.95</v>
       </c>
       <c r="I9" t="n">
         <v>408.0233526935064</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K9" t="n">
-        <v>9.01</v>
+        <v>-9.23</v>
       </c>
       <c r="L9" t="n">
-        <v>4.54</v>
+        <v>12.56</v>
       </c>
       <c r="M9" t="n">
-        <v>2.24</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>20.04</v>
       </c>
       <c r="O9" t="n">
         <v>-3.41</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43425</v>
+        <v>43426</v>
       </c>
       <c r="H10" t="n">
-        <v>401.7</v>
+        <v>398.4</v>
       </c>
       <c r="I10" t="n">
         <v>398.4285758864339</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.66</v>
+        <v>-13.38</v>
       </c>
       <c r="L10" t="n">
         <v>14.12</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.59</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H11" t="n">
-        <v>335.4</v>
+        <v>342.6</v>
       </c>
       <c r="I11" t="n">
         <v>341.7818494861516</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K11" t="n">
-        <v>15.81</v>
+        <v>14.01</v>
       </c>
       <c r="L11" t="n">
         <v>8.56</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.02</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H12" t="n">
-        <v>342.8</v>
+        <v>339.85</v>
       </c>
       <c r="I12" t="n">
         <v>342.017755838796</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06</v>
+        <v>-0.8</v>
       </c>
       <c r="L12" t="n">
         <v>3.44</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.23</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H13" t="n">
-        <v>334.2</v>
+        <v>339.4</v>
       </c>
       <c r="I13" t="n">
         <v>339.0982352288521</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="n">
-        <v>1.66</v>
+        <v>0.13</v>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="M13" t="n">
         <v>2.12</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.69</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43677</v>
+        <v>43678</v>
       </c>
       <c r="H14" t="n">
-        <v>330.6</v>
+        <v>325.95</v>
       </c>
       <c r="I14" t="n">
         <v>329.4024302408651</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.59</v>
+        <v>-3.96</v>
       </c>
       <c r="L14" t="n">
-        <v>2.77</v>
+        <v>4.54</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43713</v>
+        <v>43714</v>
       </c>
       <c r="H15" t="n">
-        <v>330</v>
+        <v>336.7</v>
       </c>
       <c r="I15" t="n">
         <v>334.6738228862564</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.24</v>
+        <v>-3.3</v>
       </c>
       <c r="L15" t="n">
         <v>4.31</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.51</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43818</v>
+        <v>43819</v>
       </c>
       <c r="H16" t="n">
-        <v>367.7</v>
+        <v>362.3</v>
       </c>
       <c r="I16" t="n">
         <v>364.0778569229547</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K16" t="n">
-        <v>9.210000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
         <v>2.14</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43840</v>
+        <v>43843</v>
       </c>
       <c r="H17" t="n">
-        <v>368.2</v>
+        <v>401.7</v>
       </c>
       <c r="I17" t="n">
         <v>386.8590641133785</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.63</v>
+        <v>-10.87</v>
       </c>
       <c r="L17" t="n">
-        <v>4.46</v>
+        <v>11.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0.66</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>1.98</v>
+        <v>9.1</v>
       </c>
       <c r="O17" t="n">
         <v>-1.47</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.61</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H18" t="n">
-        <v>402.05</v>
+        <v>384.6</v>
       </c>
       <c r="I18" t="n">
         <v>385.946467709909</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>0.09</v>
+        <v>-4.26</v>
       </c>
       <c r="L18" t="n">
         <v>6.5</v>
@@ -1467,7 +1682,7 @@
         <v>1.67</v>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>4.34</v>
       </c>
       <c r="O18" t="n">
         <v>9.1</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.63</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43978</v>
+        <v>43979</v>
       </c>
       <c r="H19" t="n">
-        <v>264.6</v>
+        <v>277.8</v>
       </c>
       <c r="I19" t="n">
         <v>277.7675225800926</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K19" t="n">
-        <v>31.2</v>
+        <v>27.77</v>
       </c>
       <c r="L19" t="n">
         <v>7.25</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44069</v>
+        <v>44070</v>
       </c>
       <c r="H20" t="n">
-        <v>588.8</v>
+        <v>505.4</v>
       </c>
       <c r="I20" t="n">
         <v>525.3001454784423</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
-        <v>111.95</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>4.34</v>
       </c>
       <c r="M20" t="n">
-        <v>6.43</v>
+        <v>11.59</v>
       </c>
       <c r="N20" t="n">
-        <v>4.48</v>
+        <v>14.16</v>
       </c>
       <c r="O20" t="n">
         <v>4.99</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>26.97</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H21" t="n">
-        <v>365.7</v>
+        <v>377.8</v>
       </c>
       <c r="I21" t="n">
         <v>366.7934854743902</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21" t="n">
-        <v>27.64</v>
+        <v>25.25</v>
       </c>
       <c r="L21" t="n">
         <v>5.45</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.19</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H22" t="n">
-        <v>431.9</v>
+        <v>399.5</v>
       </c>
       <c r="I22" t="n">
         <v>405.7295449058792</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>14.32</v>
+        <v>5.74</v>
       </c>
       <c r="L22" t="n">
         <v>4.31</v>
@@ -1695,7 +1958,7 @@
         <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>7.5</v>
       </c>
       <c r="O22" t="n">
         <v>3.31</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>14.7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H23" t="n">
-        <v>428.4</v>
+        <v>443.45</v>
       </c>
       <c r="I23" t="n">
         <v>439.5630847996169</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.23</v>
+        <v>-11</v>
       </c>
       <c r="L23" t="n">
-        <v>9.1</v>
+        <v>11.51</v>
       </c>
       <c r="M23" t="n">
         <v>1.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>3.51</v>
       </c>
       <c r="O23" t="n">
         <v>-7.5</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H24" t="n">
-        <v>510.45</v>
+        <v>501.3</v>
       </c>
       <c r="I24" t="n">
         <v>502.5859500635832</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K24" t="n">
-        <v>15.11</v>
+        <v>13.05</v>
       </c>
       <c r="L24" t="n">
         <v>3.39</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H25" t="n">
-        <v>505.25</v>
+        <v>512.7</v>
       </c>
       <c r="I25" t="n">
         <v>511.1875697281583</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.79</v>
+        <v>-2.27</v>
       </c>
       <c r="L25" t="n">
         <v>4.93</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H26" t="n">
-        <v>685.65</v>
+        <v>663.6</v>
       </c>
       <c r="I26" t="n">
         <v>672.5066759843039</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K26" t="n">
-        <v>33.73</v>
+        <v>29.43</v>
       </c>
       <c r="L26" t="n">
         <v>3.34</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.78</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H27" t="n">
-        <v>640.1</v>
+        <v>656.3</v>
       </c>
       <c r="I27" t="n">
         <v>654.9052289627617</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K27" t="n">
-        <v>3.54</v>
+        <v>1.1</v>
       </c>
       <c r="L27" t="n">
         <v>9.699999999999999</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44610</v>
+        <v>44613</v>
       </c>
       <c r="H28" t="n">
-        <v>673</v>
+        <v>650.5</v>
       </c>
       <c r="I28" t="n">
         <v>653.1947583971144</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>2.54</v>
+        <v>-0.88</v>
       </c>
       <c r="L28" t="n">
         <v>2.09</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.73</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H29" t="n">
-        <v>688.4</v>
+        <v>731.1</v>
       </c>
       <c r="I29" t="n">
         <v>705.1396394153847</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.83</v>
+        <v>-12.39</v>
       </c>
       <c r="L29" t="n">
-        <v>9.92</v>
+        <v>13.84</v>
       </c>
       <c r="M29" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="N29" t="n">
-        <v>5.57</v>
+        <v>6.2</v>
       </c>
       <c r="O29" t="n">
         <v>-3.34</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.29</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H30" t="n">
-        <v>778.5</v>
+        <v>758.5</v>
       </c>
       <c r="I30" t="n">
         <v>766.786022194712</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>6.48</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>5.55</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>12.33</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44700</v>
+        <v>44701</v>
       </c>
       <c r="H31" t="n">
-        <v>842.9</v>
+        <v>878.6</v>
       </c>
       <c r="I31" t="n">
         <v>847.555528628613</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.13</v>
+        <v>-15.83</v>
       </c>
       <c r="L31" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="N31" t="n">
         <v>5.99</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.53</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H32" t="n">
-        <v>949.35</v>
+        <v>862.4</v>
       </c>
       <c r="I32" t="n">
         <v>865.0445645412102</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K32" t="n">
-        <v>8.050000000000001</v>
+        <v>-1.84</v>
       </c>
       <c r="L32" t="n">
-        <v>2.93</v>
+        <v>3.26</v>
       </c>
       <c r="M32" t="n">
         <v>1.74</v>
       </c>
       <c r="N32" t="n">
-        <v>3.33</v>
+        <v>9.16</v>
       </c>
       <c r="O32" t="n">
         <v>4.24</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>22.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H33" t="n">
-        <v>934.5</v>
+        <v>951.7</v>
       </c>
       <c r="I33" t="n">
         <v>940.214524371294</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.359999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="L33" t="n">
         <v>12.53</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H34" t="n">
-        <v>1219.4</v>
+        <v>1169.8</v>
       </c>
       <c r="I34" t="n">
         <v>1195.432023499602</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K34" t="n">
-        <v>28.13</v>
+        <v>22.92</v>
       </c>
       <c r="L34" t="n">
         <v>1.86</v>
@@ -2379,7 +2786,7 @@
         <v>1.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.16</v>
+        <v>4.07</v>
       </c>
       <c r="O34" t="n">
         <v>1.84</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>11.64</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44868</v>
+        <v>44869</v>
       </c>
       <c r="H35" t="n">
-        <v>1272.6</v>
+        <v>1280.5</v>
       </c>
       <c r="I35" t="n">
         <v>1273.454431749344</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>9.720000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="M35" t="n">
         <v>1.33</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H36" t="n">
-        <v>1301.9</v>
+        <v>1293.2</v>
       </c>
       <c r="I36" t="n">
         <v>1301.133909607627</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>1.67</v>
+        <v>0.99</v>
       </c>
       <c r="L36" t="n">
         <v>5.85</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H37" t="n">
-        <v>1241.3</v>
+        <v>1332.7</v>
       </c>
       <c r="I37" t="n">
         <v>1299.239337465463</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K37" t="n">
-        <v>4.01</v>
+        <v>-3.05</v>
       </c>
       <c r="L37" t="n">
-        <v>3.44</v>
+        <v>4.78</v>
       </c>
       <c r="M37" t="n">
         <v>0.87</v>
       </c>
       <c r="N37" t="n">
-        <v>3.59</v>
+        <v>7.36</v>
       </c>
       <c r="O37" t="n">
         <v>-0.67</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>12.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45007</v>
+        <v>45008</v>
       </c>
       <c r="H38" t="n">
-        <v>1312.4</v>
+        <v>1248.2</v>
       </c>
       <c r="I38" t="n">
         <v>1305.530410045099</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.52</v>
+        <v>-6.34</v>
       </c>
       <c r="L38" t="n">
-        <v>6.77</v>
+        <v>7.14</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4</v>
+        <v>5.02</v>
       </c>
       <c r="N38" t="n">
         <v>5.51</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.62</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H39" t="n">
-        <v>1383.9</v>
+        <v>1408.1</v>
       </c>
       <c r="I39" t="n">
         <v>1405.712422676231</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.87</v>
+        <v>-12.81</v>
       </c>
       <c r="L39" t="n">
         <v>14</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H40" t="n">
-        <v>1957.7</v>
+        <v>1935</v>
       </c>
       <c r="I40" t="n">
         <v>1935.067150194519</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K40" t="n">
-        <v>39.03</v>
+        <v>37.42</v>
       </c>
       <c r="L40" t="n">
         <v>2.69</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.34</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H41" t="n">
-        <v>1934.75</v>
+        <v>2017.15</v>
       </c>
       <c r="I41" t="n">
         <v>1939.154747155555</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01</v>
+        <v>-4.25</v>
       </c>
       <c r="L41" t="n">
-        <v>2.84</v>
+        <v>4.55</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>4.26</v>
       </c>
       <c r="O41" t="n">
         <v>-1.16</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.84</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H42" t="n">
-        <v>3267.55</v>
+        <v>3039.5</v>
       </c>
       <c r="I42" t="n">
         <v>3118.704423902633</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K42" t="n">
-        <v>61.99</v>
+        <v>50.68</v>
       </c>
       <c r="L42" t="n">
         <v>4.32</v>
@@ -2835,7 +3338,7 @@
         <v>1.22</v>
       </c>
       <c r="N42" t="n">
-        <v>4.36</v>
+        <v>6.98</v>
       </c>
       <c r="O42" t="n">
         <v>4.26</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>14.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H43" t="n">
-        <v>3327</v>
+        <v>3403.35</v>
       </c>
       <c r="I43" t="n">
         <v>3360.516021001085</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.460000000000001</v>
+        <v>-11.97</v>
       </c>
       <c r="L43" t="n">
-        <v>10.05</v>
+        <v>13.65</v>
       </c>
       <c r="M43" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="N43" t="n">
         <v>4.73</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.16</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H44" t="n">
-        <v>5273.65</v>
+        <v>4333.35</v>
       </c>
       <c r="I44" t="n">
         <v>4639.687981379084</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K44" t="n">
-        <v>54.95</v>
+        <v>27.33</v>
       </c>
       <c r="L44" t="n">
         <v>1.21</v>
       </c>
       <c r="M44" t="n">
-        <v>0.47</v>
+        <v>2.44</v>
       </c>
       <c r="N44" t="n">
-        <v>2.66</v>
+        <v>17.83</v>
       </c>
       <c r="O44" t="n">
         <v>2.29</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>27.91</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45457</v>
+        <v>45461</v>
       </c>
       <c r="H45" t="n">
-        <v>5200.55</v>
+        <v>5533.45</v>
       </c>
       <c r="I45" t="n">
         <v>5236.652235082942</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-20.01</v>
+        <v>-27.69</v>
       </c>
       <c r="L45" t="n">
-        <v>21.38</v>
+        <v>28.47</v>
       </c>
       <c r="M45" t="n">
-        <v>2.03</v>
+        <v>4.99</v>
       </c>
       <c r="N45" t="n">
         <v>6.91</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>15.95</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H46" t="n">
-        <v>5329.4</v>
+        <v>5015.75</v>
       </c>
       <c r="I46" t="n">
         <v>5093.351295360273</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.69</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>7.57</v>
+        <v>10.09</v>
       </c>
       <c r="M46" t="n">
         <v>0.39</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>5.89</v>
       </c>
       <c r="O46" t="n">
         <v>6.4</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.72</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45580</v>
+        <v>45581</v>
       </c>
       <c r="H47" t="n">
-        <v>4575.4</v>
+        <v>4656.25</v>
       </c>
       <c r="I47" t="n">
         <v>4594.589886913004</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K47" t="n">
-        <v>8.779999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="L47" t="n">
         <v>6.17</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H48" t="n">
-        <v>4301.7</v>
+        <v>4233.75</v>
       </c>
       <c r="I48" t="n">
         <v>4272.202001378159</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.61</v>
+        <v>-9.07</v>
       </c>
       <c r="L48" t="n">
-        <v>7.86</v>
+        <v>9.98</v>
       </c>
       <c r="M48" t="n">
         <v>0.55</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H49" t="n">
-        <v>4364.55</v>
+        <v>4474.65</v>
       </c>
       <c r="I49" t="n">
         <v>4454.395042414406</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.09</v>
+        <v>-5.69</v>
       </c>
       <c r="L49" t="n">
         <v>6.05</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>11.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H50" t="n">
-        <v>4482.85</v>
+        <v>4385.1</v>
       </c>
       <c r="I50" t="n">
         <v>4411.363216977616</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K50" t="n">
-        <v>0.18</v>
+        <v>-2</v>
       </c>
       <c r="L50" t="n">
         <v>2.67</v>
       </c>
       <c r="M50" t="n">
-        <v>0.18</v>
+        <v>1.86</v>
       </c>
       <c r="N50" t="n">
         <v>3.02</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.53</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="H51" t="n">
-        <v>4116.6</v>
+        <v>4187.5</v>
       </c>
       <c r="I51" t="n">
         <v>4163.103841911642</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K51" t="n">
-        <v>6.12</v>
+        <v>4.51</v>
       </c>
       <c r="L51" t="n">
         <v>1.32</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H52" t="n">
-        <v>3849.8</v>
+        <v>3670.65</v>
       </c>
       <c r="I52" t="n">
         <v>3795.491874246413</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.06</v>
+        <v>-12.34</v>
       </c>
       <c r="L52" t="n">
-        <v>8.779999999999999</v>
+        <v>12.69</v>
       </c>
       <c r="M52" t="n">
-        <v>-0</v>
+        <v>0.85</v>
       </c>
       <c r="N52" t="n">
-        <v>3.64</v>
+        <v>4.65</v>
       </c>
       <c r="O52" t="n">
         <v>1.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>13.69</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H53" t="n">
-        <v>3439.9</v>
+        <v>3579.95</v>
       </c>
       <c r="I53" t="n">
         <v>3553.436838668176</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>6.29</v>
+        <v>2.47</v>
       </c>
       <c r="L53" t="n">
         <v>10.41</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>12.21</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="H54" t="n">
-        <v>4789.3</v>
+        <v>4651.7</v>
       </c>
       <c r="I54" t="n">
         <v>4730.740380320715</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K54" t="n">
-        <v>33.78</v>
+        <v>29.94</v>
       </c>
       <c r="L54" t="n">
         <v>3.06</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.06</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H55" t="n">
-        <v>4581.2</v>
+        <v>4745.6</v>
       </c>
       <c r="I55" t="n">
         <v>4666.180857600384</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K55" t="n">
-        <v>1.52</v>
+        <v>-2.02</v>
       </c>
       <c r="L55" t="n">
         <v>3.4</v>
@@ -3576,7 +4235,7 @@
         <v>3.31</v>
       </c>
       <c r="N55" t="n">
-        <v>2.61</v>
+        <v>3.59</v>
       </c>
       <c r="O55" t="n">
         <v>-2.87</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>7.78</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H56" t="n">
-        <v>4685.8</v>
+        <v>4593.6</v>
       </c>
       <c r="I56" t="n">
         <v>4629.911764377545</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.26</v>
+        <v>-3.2</v>
       </c>
       <c r="L56" t="n">
-        <v>3.46</v>
+        <v>3.59</v>
       </c>
       <c r="M56" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="N56" t="n">
         <v>2.19</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.8</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="H57" t="n">
-        <v>4789.8</v>
+        <v>4862.6</v>
       </c>
       <c r="I57" t="n">
         <v>4820.680796600404</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.27</v>
+        <v>-5.86</v>
       </c>
       <c r="L57" t="n">
-        <v>4.38</v>
+        <v>6.19</v>
       </c>
       <c r="M57" t="n">
         <v>0.53</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.1</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H58" t="n">
-        <v>4595</v>
+        <v>4445.1</v>
       </c>
       <c r="I58" t="n">
         <v>4565.793054753673</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.5</v>
+        <v>-8.59</v>
       </c>
       <c r="L58" t="n">
-        <v>5.71</v>
+        <v>9.41</v>
       </c>
       <c r="M58" t="n">
-        <v>0.26</v>
+        <v>3.7</v>
       </c>
       <c r="N58" t="n">
-        <v>2.58</v>
+        <v>3.26</v>
       </c>
       <c r="O58" t="n">
         <v>1.52</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.36</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H59" t="n">
-        <v>4417.8</v>
+        <v>4526.1</v>
       </c>
       <c r="I59" t="n">
         <v>4496.150525016503</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K59" t="n">
-        <v>0.61</v>
+        <v>-1.82</v>
       </c>
       <c r="L59" t="n">
         <v>3.12</v>
@@ -3804,7 +4511,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="O59" t="n">
         <v>-3.26</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>6.5</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H60" t="n">
-        <v>4355.2</v>
+        <v>4259.4</v>
       </c>
       <c r="I60" t="n">
         <v>4274.534201012688</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.78</v>
+        <v>-5.89</v>
       </c>
       <c r="L60" t="n">
-        <v>4.4</v>
+        <v>6.43</v>
       </c>
       <c r="M60" t="n">
-        <v>0.29</v>
+        <v>0.92</v>
       </c>
       <c r="N60" t="n">
         <v>3.31</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.23</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H61" t="n">
-        <v>4348.5</v>
+        <v>4624</v>
       </c>
       <c r="I61" t="n">
         <v>4610.028335313489</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.09</v>
+        <v>-8.56</v>
       </c>
       <c r="L61" t="n">
-        <v>2.77</v>
+        <v>8.9</v>
       </c>
       <c r="M61" t="n">
         <v>1.03</v>
       </c>
       <c r="N61" t="n">
-        <v>2.2</v>
+        <v>6.34</v>
       </c>
       <c r="O61" t="n">
         <v>-2.2</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.71</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H62" t="n">
-        <v>4470.4</v>
+        <v>4217.1</v>
       </c>
       <c r="I62" t="n">
         <v>4242.527727280738</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.32</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>9.93</v>
+        <v>11.38</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="N62" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="O62" t="n">
         <v>6.34</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>15.14</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H63" t="n">
-        <v>3796.2</v>
+        <v>3907.5</v>
       </c>
       <c r="I63" t="n">
         <v>3890.460974239013</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K63" t="n">
-        <v>9.98</v>
+        <v>7.34</v>
       </c>
       <c r="L63" t="n">
         <v>4.65</v>
       </c>
       <c r="M63" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="N63" t="n">
         <v>5.26</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.03</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H64" t="n">
-        <v>4608</v>
+        <v>4386.2</v>
       </c>
       <c r="I64" t="n">
         <v>4438.345918676115</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K64" t="n">
-        <v>17.93</v>
+        <v>12.25</v>
       </c>
       <c r="L64" t="n">
         <v>1.47</v>
@@ -4089,7 +4856,7 @@
         <v>1.76</v>
       </c>
       <c r="N64" t="n">
-        <v>3.86</v>
+        <v>4.81</v>
       </c>
       <c r="O64" t="n">
         <v>2.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.64</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H65" t="n">
-        <v>4408.1</v>
+        <v>4515.2</v>
       </c>
       <c r="I65" t="n">
         <v>4502.559707792816</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.5</v>
+        <v>-2.94</v>
       </c>
       <c r="L65" t="n">
         <v>5.28</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.68</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H66" t="n">
-        <v>4905</v>
+        <v>4695</v>
       </c>
       <c r="I66" t="n">
         <v>4742.083811742052</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K66" t="n">
-        <v>8.630000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="L66" t="n">
         <v>5.43</v>
@@ -4203,7 +4994,7 @@
         <v>0.92</v>
       </c>
       <c r="N66" t="n">
-        <v>2.92</v>
+        <v>4.28</v>
       </c>
       <c r="O66" t="n">
         <v>2.43</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.26</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="H67" t="n">
-        <v>4910</v>
+        <v>4989</v>
       </c>
       <c r="I67" t="n">
         <v>4957.625247210713</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.58</v>
+        <v>-6.26</v>
       </c>
       <c r="L67" t="n">
-        <v>5.45</v>
+        <v>6.26</v>
       </c>
       <c r="M67" t="n">
         <v>1.99</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,14 @@
       <c r="Q68" t="n">
         <v>8</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7986,7 +8809,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="6">
@@ -7996,7 +8819,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="7">
@@ -8006,7 +8829,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
@@ -8016,7 +8839,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8026,7 +8849,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60.8</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="10">
@@ -8036,7 +8859,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94.5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -8046,7 +8869,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -8056,7 +8879,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -8066,7 +8889,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -8076,7 +8899,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.31</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15">
@@ -8086,7 +8909,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.42</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="16">
@@ -8096,7 +8919,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="17">
@@ -8106,7 +8929,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111.95</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -8116,7 +8939,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="19">
@@ -8126,7 +8949,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.99</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="20">
@@ -8136,7 +8959,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.79</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="21">
@@ -8146,7 +8969,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.38</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="22">
@@ -8156,7 +8979,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -8166,7 +8989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -8176,7 +8999,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="25">
@@ -8186,7 +9009,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.859999999999999</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="26">
@@ -8196,7 +9019,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.79</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="27">
@@ -8206,7 +9029,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.76</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="28">
@@ -8216,7 +9039,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
